--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_coquimbo.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:47</t>
+    <t xml:space="preserve">2026-09-24 00:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.58</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0.13</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.73</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="9">
@@ -716,13 +716,13 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.07</v>
+        <v>0.02</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0.15</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="10">
@@ -739,13 +739,13 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.74</v>
+        <v>-0.69</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.78</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="11">
@@ -762,13 +762,13 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.68</v>
+        <v>-0.6</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.06</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="12">
@@ -969,13 +969,13 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.59</v>
+        <v>-0.57</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0.12</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-0.71</v>
+        <v>-0.69</v>
       </c>
     </row>
     <row r="21">
@@ -992,13 +992,13 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="22">
@@ -1015,13 +1015,13 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.75</v>
+        <v>-0.69</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0.03</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.78</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="23">
@@ -1038,13 +1038,13 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.69</v>
+        <v>-0.61</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.61</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="24">
@@ -1245,13 +1245,13 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>0.2</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="33">
@@ -1268,13 +1268,13 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.16</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="34">
@@ -1291,13 +1291,13 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="35">
@@ -1314,13 +1314,13 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.49</v>
+        <v>0.35</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.36</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="36">
@@ -1521,13 +1521,13 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>0.24</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="45">
@@ -1544,13 +1544,13 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="46">
@@ -1567,13 +1567,13 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.08</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="47">
@@ -1590,13 +1590,13 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="48">
@@ -1797,13 +1797,13 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>0.07</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="57">
@@ -1823,10 +1823,10 @@
         <v>-0.51</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="58">
@@ -1866,13 +1866,13 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="60">
@@ -2073,13 +2073,13 @@
         <v>18</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.24</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>-0.05</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="69">
@@ -2096,13 +2096,13 @@
         <v>18</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>-0.06</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="70">
@@ -2119,13 +2119,13 @@
         <v>18</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="71">
@@ -2142,13 +2142,13 @@
         <v>18</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="72">
@@ -2349,13 +2349,13 @@
         <v>18</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.48</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="81">
@@ -2372,13 +2372,13 @@
         <v>18</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>-0.61</v>
+        <v>-0.59</v>
       </c>
       <c r="F81" s="2" t="n">
         <v>-0.38</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="82">
@@ -2395,7 +2395,7 @@
         <v>18</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>-0.04</v>
@@ -2418,13 +2418,13 @@
         <v>18</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="F83" s="2" t="n">
         <v>0.15</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="84">
@@ -2625,13 +2625,13 @@
         <v>18</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.52</v>
       </c>
       <c r="F92" s="2" t="n">
         <v>-0.38</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="93">
@@ -2648,13 +2648,13 @@
         <v>18</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.45</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="94">
@@ -2671,13 +2671,13 @@
         <v>18</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="F94" s="2" t="n">
         <v>-0.21</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="95">
@@ -2694,13 +2694,13 @@
         <v>18</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="96">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_coquimbo.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:38</t>
+    <t xml:space="preserve">2026-10-01 23:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_coquimbo.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:10</t>
+    <t xml:space="preserve">2026-10-05 19:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
